--- a/AAII_Financials/Quarterly/LNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>LNC</t>
   </si>
@@ -656,316 +656,322 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5034000</v>
+        <v>4579000</v>
       </c>
       <c r="E8" s="3">
+        <v>5332000</v>
+      </c>
+      <c r="F8" s="3">
         <v>4889000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4594000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4068000</v>
       </c>
-      <c r="H8" s="3">
-        <v>4473000</v>
-      </c>
       <c r="I8" s="3">
+        <v>4719000</v>
+      </c>
+      <c r="J8" s="3">
         <v>5046000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4201000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4605000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4116000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>720000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4228000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2935000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3819000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5408000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5470000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5100000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6079000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5235000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5241000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4851000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4534000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4136000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5361000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3517000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4425000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4346000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4640000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4314000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3973000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4542000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4278000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4028000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3619000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3626000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3532000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3593000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3522000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3339000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3532000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5517000</v>
+        <v>4331000</v>
       </c>
       <c r="E9" s="3">
+        <v>4529000</v>
+      </c>
+      <c r="F9" s="3">
         <v>977000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3951000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4237000</v>
       </c>
-      <c r="H9" s="3">
-        <v>5619000</v>
-      </c>
       <c r="I9" s="3">
+        <v>4325000</v>
+      </c>
+      <c r="J9" s="3">
         <v>1993000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4778000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4211000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4425000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>-1843000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4354000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4376000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4401000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-483000</v>
+        <v>248000</v>
       </c>
       <c r="E10" s="3">
+        <v>803000</v>
+      </c>
+      <c r="F10" s="3">
         <v>3912000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>643000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-169000</v>
       </c>
-      <c r="H10" s="3">
-        <v>-1146000</v>
-      </c>
       <c r="I10" s="3">
+        <v>394000</v>
+      </c>
+      <c r="J10" s="3">
         <v>3053000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-577000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>394000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-309000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2563000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-126000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1441000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-582000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,79 +1467,82 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>6000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>60000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>40000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-584000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>34000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>634000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>14000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1532,49 +1551,52 @@
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>8000</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>2000</v>
       </c>
       <c r="AH14" s="3">
         <v>2000</v>
       </c>
       <c r="AI14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>2000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>906000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>9000</v>
-      </c>
-      <c r="AM14" s="3">
-        <v>4000</v>
       </c>
       <c r="AN14" s="3">
         <v>4000</v>
       </c>
       <c r="AO14" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AP14" s="3">
         <v>32000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1582,11 +1604,11 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>148000</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
@@ -1594,10 +1616,10 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>96000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>2300</v>
       </c>
       <c r="K15" s="3">
         <v>2300</v>
@@ -1606,10 +1628,10 @@
         <v>2300</v>
       </c>
       <c r="M15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N15" s="3">
         <v>44000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>5800</v>
       </c>
       <c r="O15" s="3">
         <v>5800</v>
@@ -1618,7 +1640,7 @@
         <v>5800</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1632,8 +1654,8 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>5</v>
@@ -1653,35 +1675,35 @@
       <c r="AB15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC15" s="3">
-        <v>15000</v>
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD15" s="3">
         <v>15000</v>
       </c>
       <c r="AE15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>19000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>18000</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI15" s="3">
         <v>2000</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>1000</v>
       </c>
       <c r="AJ15" s="3">
         <v>1000</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL15" s="3">
+      <c r="AK15" s="3">
         <v>1000</v>
+      </c>
+      <c r="AL15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AM15" s="3">
         <v>1000</v>
@@ -1689,14 +1711,17 @@
       <c r="AN15" s="3">
         <v>1000</v>
       </c>
-      <c r="AO15" s="3" t="s">
-        <v>5</v>
+      <c r="AO15" s="3">
+        <v>1000</v>
       </c>
       <c r="AP15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5239000</v>
+        <v>4368000</v>
       </c>
       <c r="E17" s="3">
+        <v>4549000</v>
+      </c>
+      <c r="F17" s="3">
         <v>4250000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3990000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4261000</v>
       </c>
-      <c r="H17" s="3">
-        <v>5401000</v>
-      </c>
       <c r="I17" s="3">
+        <v>4353000</v>
+      </c>
+      <c r="J17" s="3">
         <v>5524000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4866000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4247000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4425000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1735000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4379000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4382000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4406000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4296000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7481000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3956000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4147000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4292000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4784000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3993000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4194000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3958000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4815000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3580000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4311000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3772000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4761000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3808000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3619000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3977000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3657000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3489000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3072000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3935000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2943000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2976000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2966000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2950000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2862000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-205000</v>
+        <v>211000</v>
       </c>
       <c r="E18" s="3">
+        <v>783000</v>
+      </c>
+      <c r="F18" s="3">
         <v>639000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>604000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-193000</v>
       </c>
-      <c r="H18" s="3">
-        <v>-928000</v>
-      </c>
       <c r="I18" s="3">
+        <v>366000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-478000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-665000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>358000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-309000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1015000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-151000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1447000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-587000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1112000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2011000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1144000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1932000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>943000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>457000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>858000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>340000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>178000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>546000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-63000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>114000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>574000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-121000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>506000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>354000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>565000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>621000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>539000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>547000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-309000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>589000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>617000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>556000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>389000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,175 +2056,179 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-46000</v>
+        <v>-1514000</v>
       </c>
       <c r="E20" s="3">
+        <v>941000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-417000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1041000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-59000</v>
-      </c>
       <c r="I20" s="3">
+        <v>1248000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2701000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-50000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-240000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1919000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>484000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1269000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2133000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>501000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>29000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-44000</v>
       </c>
       <c r="S20" s="3">
         <v>-44000</v>
       </c>
       <c r="T20" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="U20" s="3">
         <v>-31000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-30000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-22000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-21000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-23000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-14000</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-15000</v>
       </c>
       <c r="AF20" s="3">
         <v>-15000</v>
       </c>
       <c r="AG20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-15000</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>-10000</v>
       </c>
       <c r="AL20" s="3">
         <v>-10000</v>
       </c>
       <c r="AM20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-14000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-8000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-159000</v>
+        <v>1725000</v>
       </c>
       <c r="E21" s="3">
+        <v>-158000</v>
+      </c>
+      <c r="F21" s="3">
         <v>1204000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>603000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>848000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-869000</v>
-      </c>
       <c r="I21" s="3">
+        <v>-882000</v>
+      </c>
+      <c r="J21" s="3">
         <v>2319000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-612800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>600300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1612300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1455000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1123800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>691800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1082300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2238,404 +2274,416 @@
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>549000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>604000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>523000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>533000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-319000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>579000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>603000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>548000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>381000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>670000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>82000</v>
+      </c>
+      <c r="F22" s="3">
         <v>81000</v>
       </c>
-      <c r="E22" s="3">
-        <v>81000</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>79000</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="3">
-        <v>80000</v>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I22" s="3">
+        <v>67000</v>
+      </c>
+      <c r="J22" s="3">
         <v>83000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>86000</v>
       </c>
       <c r="K22" s="3">
         <v>86000</v>
       </c>
       <c r="L22" s="3">
-        <v>81000</v>
+        <v>86000</v>
       </c>
       <c r="M22" s="3">
         <v>81000</v>
       </c>
       <c r="N22" s="3">
-        <v>84000</v>
+        <v>81000</v>
       </c>
       <c r="O22" s="3">
         <v>84000</v>
       </c>
       <c r="P22" s="3">
+        <v>84000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>82000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>156000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>71000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>68000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>66000</v>
       </c>
       <c r="U22" s="3">
         <v>66000</v>
       </c>
       <c r="V22" s="3">
+        <v>66000</v>
+      </c>
+      <c r="W22" s="3">
         <v>67000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>65000</v>
       </c>
       <c r="X22" s="3">
         <v>65000</v>
       </c>
       <c r="Y22" s="3">
-        <v>66000</v>
+        <v>65000</v>
       </c>
       <c r="Z22" s="3">
         <v>66000</v>
       </c>
       <c r="AA22" s="3">
+        <v>66000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>84000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>65000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>74000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>115000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>70000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>71000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>78000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>71000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>72000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>97000</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>69000</v>
       </c>
       <c r="AL22" s="3">
         <v>69000</v>
       </c>
       <c r="AM22" s="3">
+        <v>69000</v>
+      </c>
+      <c r="AN22" s="3">
         <v>70000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>72000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>185000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>58000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1643000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-246000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>915000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>524000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>848000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-949000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2100000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-703000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1096000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1529000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1614000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1034000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>602000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1170000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>985000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2126000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1032000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1835000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>847000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>368000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>772000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>262000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>89000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>460000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-161000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>34000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>481000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-250000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>421000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>268000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>467000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>532000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>451000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>435000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-388000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>510000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>533000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>475000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>196000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>612000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>311000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-74000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>161000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>79000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>149000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-227000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>413000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-175000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>201000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>308000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-379000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>181000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>91000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-289000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>172000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-350000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>192000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>353000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>145000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>50000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>130000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>37000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-17000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>62000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-67000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>66000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-89000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>58000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>16000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>106000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>10000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>66000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>81000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>97000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>92000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>122000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>40000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>3000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>145000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-172000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>754000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>445000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>699000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-722000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1687000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-528000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>895000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1221000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1235000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>853000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>511000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-881000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>813000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1776000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>840000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1482000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>702000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>318000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>642000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>225000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>106000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>398000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-94000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>52000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>415000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-161000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>363000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>252000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>361000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>522000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>385000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>354000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-485000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>418000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>411000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>435000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>193000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>467000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-206000</v>
+        <v>1321000</v>
       </c>
       <c r="E27" s="3">
+        <v>-207000</v>
+      </c>
+      <c r="F27" s="3">
         <v>743000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>411000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>688000</v>
       </c>
-      <c r="H27" s="3">
-        <v>-756000</v>
-      </c>
       <c r="I27" s="3">
+        <v>-757000</v>
+      </c>
+      <c r="J27" s="3">
         <v>1676000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-562000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>884000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1186000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1246000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>819000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-906000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>808000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1777000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>833000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1481000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>702000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>318000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>642000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>225000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>106000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>398000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-94000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>52000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>415000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-161000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>363000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>252000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>361000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>522000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>385000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>354000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-485000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>418000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>411000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>435000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>193000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>467000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3172,8 +3232,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
@@ -3190,24 +3250,24 @@
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
         <v>37000</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>17000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
@@ -3215,37 +3275,40 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>38000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-32000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>13000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>1300000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP29" s="3" t="s">
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>46000</v>
+        <v>1514000</v>
       </c>
       <c r="E32" s="3">
+        <v>-941000</v>
+      </c>
+      <c r="F32" s="3">
         <v>417000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1041000</v>
       </c>
-      <c r="H32" s="3">
-        <v>59000</v>
-      </c>
       <c r="I32" s="3">
+        <v>-1248000</v>
+      </c>
+      <c r="J32" s="3">
         <v>2701000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>50000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>240000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1919000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-484000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1269000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2133000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-501000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-29000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>44000</v>
       </c>
       <c r="S32" s="3">
         <v>44000</v>
       </c>
       <c r="T32" s="3">
+        <v>44000</v>
+      </c>
+      <c r="U32" s="3">
         <v>31000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>30000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>22000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>21000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>13000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>23000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>20000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>14000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>15000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>19000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>14000</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>15000</v>
       </c>
       <c r="AF32" s="3">
         <v>15000</v>
       </c>
       <c r="AG32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AH32" s="3">
         <v>20000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>18000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>15000</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>10000</v>
       </c>
       <c r="AL32" s="3">
         <v>10000</v>
       </c>
       <c r="AM32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AN32" s="3">
         <v>14000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>9000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>8000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-172000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>754000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>445000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>699000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-722000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1687000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-528000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>895000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1221000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1235000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>853000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>511000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-881000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>808000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1777000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>833000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1481000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>702000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>318000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>642000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>225000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>143000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>398000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-94000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>52000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>432000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-161000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>363000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>252000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>399000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>490000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>385000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>367000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>815000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>418000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>411000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>435000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>193000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>467000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-172000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>754000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>445000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>699000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-722000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1687000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-528000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>895000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1221000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1235000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>853000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>511000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-881000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>808000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1777000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>833000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1481000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>702000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>318000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>642000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>225000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>143000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>398000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-94000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>52000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>432000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-161000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>363000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>252000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>399000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>490000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>385000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>367000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>815000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>418000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>411000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>435000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>193000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>467000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10165000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7345000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9502000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10668000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7143000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4284000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5801000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6013000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5475000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4122000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3365000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2529000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3768000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3766000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3343000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1472000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1567000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1960000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2612000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2614000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2389000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1350000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1708000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2595000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4201000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6202000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2563000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2939000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3314000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1593000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2345000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1460000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1775000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2257000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1628000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1965000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1978000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1923000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2722000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3444000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>35384000</v>
+      </c>
+      <c r="E42" s="3">
         <v>35342000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>35560000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>35141000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>34391000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>33515000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>33193000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>32936000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>32319000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>31348000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>31839000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2958000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3082000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3344000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,44 +4524,47 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3">
         <v>88000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>86000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>99000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>100000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>99000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>32000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
@@ -4482,83 +4574,86 @@
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S43" s="3">
         <v>583000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>656000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>671000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>580000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>584000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>583000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>653000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>486000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>498000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>490000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>562000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>465000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>440000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>553000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>607000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>570000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>592000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>574000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>480000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>396000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>370000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>365000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>465000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>430000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>355000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41215000</v>
+      </c>
+      <c r="E45" s="3">
         <v>38529000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>42150000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41599000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>39163000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38657000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>42752000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>41049000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>39838000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40112000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>41041000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>26532000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26435000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25269000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>86764000</v>
+      </c>
+      <c r="E46" s="3">
         <v>81304000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>87298000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>87508000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>80796000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>76556000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>81845000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>79998000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>77632000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>75582000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>76277000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>32019000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>33285000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32379000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,174 +5024,180 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>102791000</v>
+      </c>
+      <c r="E47" s="3">
         <v>103224000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>100805000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>98786000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>95610000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>94812000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>93601000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>96489000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>92891000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>93122000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>93826000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>102568000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>105349000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>106164000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>130867000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>125812000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>131875000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>139784000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>148189000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>150697000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>150567000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>145106000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>150847000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>146279000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>141960000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>130835000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>131786000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>130319000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>124870000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>120764000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>114097000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>111968000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>111412000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>109209000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>112163000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>110743000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>109562000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>107618000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>105770000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>109398000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>58000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>85000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>118000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -5134,17 +5241,17 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>12000</v>
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH48" s="3">
         <v>12000</v>
       </c>
       <c r="AI48" s="3">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="AJ48" s="3">
         <v>11000</v>
@@ -5156,69 +5263,72 @@
         <v>11000</v>
       </c>
       <c r="AM48" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AN48" s="3">
         <v>23000</v>
-      </c>
-      <c r="AN48" s="3">
-        <v>24000</v>
       </c>
       <c r="AO48" s="3">
         <v>24000</v>
       </c>
       <c r="AP48" s="3">
+        <v>24000</v>
+      </c>
+      <c r="AQ48" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13852000</v>
+      </c>
+      <c r="E49" s="3">
         <v>13820000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14171000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13825000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13748000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13707000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13930000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13619000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13579000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13549000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13830000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13485000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13460000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13421000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1144000</v>
       </c>
       <c r="R49" s="3">
         <v>1144000</v>
       </c>
       <c r="S49" s="3">
-        <v>1778000</v>
+        <v>1144000</v>
       </c>
       <c r="T49" s="3">
         <v>1778000</v>
@@ -5260,22 +5370,22 @@
         <v>1778000</v>
       </c>
       <c r="AG49" s="3">
+        <v>1778000</v>
+      </c>
+      <c r="AH49" s="3">
         <v>1782000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1757000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1750000</v>
-      </c>
-      <c r="AJ49" s="3">
-        <v>1368000</v>
       </c>
       <c r="AK49" s="3">
         <v>1368000</v>
       </c>
       <c r="AL49" s="3">
-        <v>2273000</v>
+        <v>1368000</v>
       </c>
       <c r="AM49" s="3">
         <v>2273000</v>
@@ -5289,8 +5399,11 @@
       <c r="AP49" s="3">
         <v>2273000</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>2273000</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,53 +5649,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200178000</v>
+      </c>
+      <c r="E52" s="3">
         <v>182172000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>189563000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>190342000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>184363000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>173736000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>177613000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>183368000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>177766000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>179386000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>166728000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>169160000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>175635000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>170468000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5655,8 +5774,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>429797000</v>
+      </c>
+      <c r="E54" s="3">
         <v>406161000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>417204000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>415275000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>399065000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>382898000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>390831000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>396840000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>384533000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>383381000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>372413000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>338411000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>348612000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>343142000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>334331000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>324683000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>335769000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>365929000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>386945000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>377052000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>380148000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>366760000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>365948000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>347804000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>339659000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>318649000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>334761000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>325278000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>322259000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>314299000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>298147000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>303850000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>298832000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>279237000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>281763000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>276785000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>271651000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>267468000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>261627000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>266605000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,52 +6116,53 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22468000</v>
+      </c>
+      <c r="E57" s="3">
         <v>23234000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23635000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23226000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>22337000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22429000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22417000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17595000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17044000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17486000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>23207000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -6109,8 +6239,11 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6118,11 +6251,11 @@
         <v>400000</v>
       </c>
       <c r="E58" s="3">
+        <v>400000</v>
+      </c>
+      <c r="F58" s="3">
         <v>426000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -6130,25 +6263,25 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>300000</v>
       </c>
       <c r="K58" s="3">
+        <v>300000</v>
+      </c>
+      <c r="L58" s="3">
         <v>475000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>503000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>250000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>500000</v>
@@ -6160,13 +6293,13 @@
         <v>500000</v>
       </c>
       <c r="S58" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>300000</v>
@@ -6178,7 +6311,7 @@
         <v>300000</v>
       </c>
       <c r="Y58" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -6190,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>300000</v>
@@ -6201,20 +6334,20 @@
       <c r="AF58" s="3">
         <v>300000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3">
+        <v>300000</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AI58" s="3">
         <v>0</v>
       </c>
       <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
         <v>250000</v>
-      </c>
-      <c r="AK58" s="3">
-        <v>450000</v>
       </c>
       <c r="AL58" s="3">
         <v>450000</v>
@@ -6223,183 +6356,189 @@
         <v>450000</v>
       </c>
       <c r="AN58" s="3">
+        <v>450000</v>
+      </c>
+      <c r="AO58" s="3">
         <v>200000</v>
       </c>
-      <c r="AO58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AP58" s="3">
+      <c r="AP58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>250000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16856000</v>
+      </c>
+      <c r="E59" s="3">
         <v>13444000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15115000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14918000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13089000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10807000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12449000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>81000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9077000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7174000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7510000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5796000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>430049000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>306240000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>309977000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>332644000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>346593000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>336366000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>338377000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>327749000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>322744000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>304311000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>295071000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>277502000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>295223000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>284167000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>283850000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>278638000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>265262000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>277551000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>273082000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>252419000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>253550000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>247302000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>242933000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>240097000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>234761000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>235341000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39724000</v>
+      </c>
+      <c r="E60" s="3">
         <v>37078000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>39176000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38144000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35426000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33236000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35166000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17895000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17519000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18070000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32534000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7174000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8010000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6296000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,175 +6614,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6841000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6312000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6627000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7772000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9120000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8737000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6927000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6182000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8916000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6813000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7488000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7464000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7046000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6949000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5955000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5959000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6498000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6561000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6325000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6323000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6334000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6294000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6682000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6714000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6736000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6748000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6067000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6070000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5621000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5572000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5839000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5804000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5826000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5648000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4894000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4900000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>4901000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5133000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5345000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5457000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>371883000</v>
+      </c>
+      <c r="E62" s="3">
         <v>352559000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>360495000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>358907000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>344971000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>332732000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>340469000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>363750000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>350149000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>350952000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>325498000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>320574000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>327737000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>323165000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6719,8 +6864,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>418448000</v>
+      </c>
+      <c r="E66" s="3">
         <v>395949000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>406298000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>404823000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>389517000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>374705000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>382562000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>387827000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>376584000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>375835000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>365520000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>335212000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>342793000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>336410000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>329229000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>322466000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>326581000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>351217000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>366191000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>355882000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>358403000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>347167000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>343249000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>326255000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>318928000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>302074000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>315072000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>305279000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>303804000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>297882000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>283797000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>288780000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>283655000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>263252000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>264441000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>260471000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>255655000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>252495000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>247149000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>250282000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7543,7 +7710,7 @@
         <v>986000</v>
       </c>
       <c r="R70" s="3">
-        <v>0</v>
+        <v>986000</v>
       </c>
       <c r="S70" s="3">
         <v>0</v>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9322000</v>
+      </c>
+      <c r="E72" s="3">
         <v>8091000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8386000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7731000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7409000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6810000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7645000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6049000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6691000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5887000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4778000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6102000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5362000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4940000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5924000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6311000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8985000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8876000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9578000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9365000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9245000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8775000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8686000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8647000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8327000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8500000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>8854000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8559000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8878000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>8679000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8551000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>8615000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8302000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8052000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>8399000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>7738000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>7511000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>7287000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>7043000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>7037000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10363000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9226000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9920000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9466000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8562000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7207000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7283000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8027000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6963000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6560000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5907000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2213000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4833000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5746000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4116000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2217000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9188000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14712000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20754000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21170000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21745000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19593000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>22699000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>21549000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20731000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16575000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19689000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>19999000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>18455000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>16417000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14350000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15070000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15177000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15985000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17322000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>16314000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>15996000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14973000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>14478000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>16323000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-172000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>754000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>445000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>699000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-722000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1687000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-528000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>895000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1221000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1235000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>853000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>511000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-881000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>808000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1777000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>833000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1481000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>702000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>318000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>642000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>225000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>143000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>398000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-94000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>52000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>432000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-161000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>363000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>252000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>399000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>490000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>385000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>367000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>815000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>418000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>411000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>435000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>193000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>467000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,8 +8961,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8796,20 +8994,20 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>23000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8886,8 +9084,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-558000</v>
+      </c>
+      <c r="E89" s="3">
         <v>138000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>233000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1141000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1013000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-272000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>222000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-27000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-859000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1343000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1868000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>46000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>522000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-774000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>642000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>686000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1955000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>753000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>60000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>339000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>411000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-642000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>193000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-630000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>516000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>455000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>171000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-295000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1231000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1331000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>909000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>402000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>492000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>140000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>179000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>407000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>93000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>109000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>595000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>144000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2578000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3454000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3913000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2212000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-266000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2046000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-717000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-702000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>601000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1639000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-714000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1438000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-857000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-325000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1783000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3115000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4608000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2140000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1131000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-918000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-806000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-712000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3036000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3081000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4106000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>742000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3214000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2226000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1074000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1133000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1867000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1778000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-595000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1404000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-780000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-505000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1499000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2054000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1372000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10209,10 +10442,10 @@
         <v>86000</v>
       </c>
       <c r="G96" s="3">
+        <v>86000</v>
+      </c>
+      <c r="H96" s="3">
         <v>76000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>77000</v>
       </c>
       <c r="I96" s="3">
         <v>77000</v>
@@ -10221,13 +10454,13 @@
         <v>77000</v>
       </c>
       <c r="K96" s="3">
+        <v>77000</v>
+      </c>
+      <c r="L96" s="3">
         <v>76000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>77000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>76000</v>
       </c>
       <c r="N96" s="3">
         <v>76000</v>
@@ -10236,88 +10469,91 @@
         <v>76000</v>
       </c>
       <c r="P96" s="3">
+        <v>76000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>77000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-76000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-77000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-78000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-79000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-78000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-80000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-81000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-80000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-78000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-77000</v>
       </c>
       <c r="AA96" s="3">
         <v>-77000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-79000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-76000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-76000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-77000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-72000</v>
       </c>
       <c r="AH96" s="3">
         <v>-72000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-73000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-72000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-64000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-66000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-65000</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-58000</v>
       </c>
       <c r="AP96" s="3">
         <v>-58000</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-58000</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1159000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2514000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2454000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2112000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>801000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>283000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1267000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1611000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>461000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3418000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>153000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>337000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1522000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3060000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2370000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2326000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1012000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1086000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>804000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1434000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>996000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1956000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2105000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1589000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2442000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2667000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2146000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1878000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1712000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1551000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1150000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>804000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1084000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>888000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>360000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>467000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>591000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>737000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>559000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2157000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1166000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3525000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2859000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1517000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-212000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>538000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1353000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>757000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>836000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1239000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>423000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1871000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-95000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-393000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-652000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>225000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1039000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-358000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-887000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1606000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2001000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3639000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-376000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-375000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1721000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-752000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>885000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-315000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-482000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>629000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-337000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-13000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>55000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-799000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-722000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-669000</v>
       </c>
     </row>
